--- a/output/quickfixclose6_portfolio_daily.xlsx
+++ b/output/quickfixclose6_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>190,565.60</t>
+          <t>214,210.75</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+90.57%</t>
+          <t>+114.21%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>197,021  (+97.02%)</t>
+          <t>221,753  (+121.75%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,764  (6.5 pts of return)</t>
+          <t>4,066  (7.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.2x</t>
+          <t>6.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.4 bars</t>
+          <t>3.5 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+5.40R  (best +16.59R)</t>
+          <t>+5.52R  (best +16.59R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,815  (+5.40%)</t>
+          <t>6,298  (+5.52%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,299  (-1.31%)</t>
+          <t>-1,316  (-1.30%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5699,22 +5699,74 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>190565.6</v>
+        <v>190742</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>7323.63</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>183418.36</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>216383.29</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>3724.14</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>212659.15</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+18,702); Corn_CBOT_Futures exit_close (+6,939)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>214210.75</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>190565.6</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>214210.75</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures stop (-2,149); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9809,14 +9861,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>10.377</v>
       </c>
       <c r="G80" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.019</v>
+        <v>10.34</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>215507.8</v>
@@ -9824,15 +9884,15 @@
       <c r="J80" s="5" t="n">
         <v>2995.56</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>-56.52</v>
+      <c r="K80" s="7" t="n">
+        <v>30973.07</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>231849.61</v>
+        <v>262879.2</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9852,14 +9912,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>3.925</v>
       </c>
       <c r="G81" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.025</v>
+        <v>3.875</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>212512.25</v>
@@ -9867,15 +9935,15 @@
       <c r="J81" s="5" t="n">
         <v>2953.92</v>
       </c>
-      <c r="K81" s="6" t="n">
-        <v>-73.84999999999999</v>
+      <c r="K81" s="7" t="n">
+        <v>11446.44</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>231775.76</v>
+        <v>274325.64</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9982,7 @@
         <v>-39.26</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>231612.61</v>
+        <v>270693.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -9938,14 +10006,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>222815.85</v>
@@ -9954,14 +10030,14 @@
         <v>3097.14</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>-123.89</v>
+        <v>-3592.68</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>231651.87</v>
+        <v>270732.96</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose6_portfolio_daily.xlsx
+++ b/output/quickfixclose6_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>214,210.75</t>
+          <t>257,802.72</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+114.21%</t>
+          <t>+157.80%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>221,753  (+121.75%)</t>
+          <t>266,817  (+166.82%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,066  (7.5 pts of return)</t>
+          <t>4,101  (9.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.6x</t>
+          <t>9.1x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+5.52R  (best +16.59R)</t>
+          <t>+6.11R  (best +23.29R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,298  (+5.52%)</t>
+          <t>7,541  (+6.11%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>76% of trading days</t>
+          <t>77% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5751,22 +5751,86 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>214210.75</v>
+        <v>214234.14</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>0</v>
+        <v>1871.42</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>214210.75</v>
+        <v>212362.72</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,149); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,149)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>257814.95</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>6307.39</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>251507.57</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,124); Nasdaq_100_E_mini short (risk 2,102); S_P_500_E_mini short (risk 2,081)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures exit_close (+43,581)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>257802.72</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>257802.72</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,515)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9963,14 +10027,22 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>23.312</v>
       </c>
       <c r="G82" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.013</v>
+        <v>23.288</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>225956.65</v>
@@ -9978,15 +10050,15 @@
       <c r="J82" s="5" t="n">
         <v>3140.8</v>
       </c>
-      <c r="K82" s="6" t="n">
-        <v>-39.26</v>
+      <c r="K82" s="7" t="n">
+        <v>73141.32000000001</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>270693.7</v>
+        <v>343874.28</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10038,6 +10110,178 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>267592.16</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>3719.53</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-12.92</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>343853.25</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>263872.63</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>3667.83</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>343866.16</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>260204.8</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>3616.85</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>343852.48</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>332870.07</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>4626.89</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-7.91</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>343866.37</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose6_portfolio_daily.xlsx
+++ b/output/quickfixclose6_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>257,802.72</t>
+          <t>255,258.35</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+157.80%</t>
+          <t>+155.26%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>266,817  (+166.82%)</t>
+          <t>264,214  (+164.21%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,101  (9.0 pts of return)</t>
+          <t>4,130  (9.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9.1x</t>
+          <t>9.0x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,316  (-1.30%)</t>
+          <t>-1,339  (-1.30%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5811,26 +5811,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>257802.72</v>
+        <v>257814.95</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>8822.459999999999</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>248992.49</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,515)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>255258.35</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>257802.72</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>255258.35</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,515)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,490); NY_Palladium_Futures short (risk 2,465)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-2,532); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10148,7 +10176,7 @@
         <v>-12.92</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>343853.25</v>
+        <v>339172.65</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10191,7 +10219,7 @@
         <v>-0.2</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>343866.16</v>
+        <v>339215.54</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10234,7 +10262,7 @@
         <v>-0.77</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>343852.48</v>
+        <v>339171.89</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -10258,14 +10286,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>332870.07</v>
@@ -10274,12 +10310,98 @@
         <v>4626.89</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>-7.91</v>
+        <v>-4658.53</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>343866.37</v>
+        <v>339215.74</v>
       </c>
       <c r="M87" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>328243.17</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>4562.58</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-12.33</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>339203.21</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>323680.59</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>4499.16</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>-17.64</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>339185.57</v>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
